--- a/DEV/org.openl.rules.test/test-resources/functionality/MultiRowDatatableAndTests.xlsx
+++ b/DEV/org.openl.rules.test/test-resources/functionality/MultiRowDatatableAndTests.xlsx
@@ -2424,7 +2424,7 @@
       <c r="G148" s="48"/>
       <c r="H148" s="48"/>
       <c r="I148" s="47">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="149" spans="2:9" x14ac:dyDescent="0.25">
